--- a/data/trans_bre/IP16A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 16,08</t>
+          <t>-10,12; 15,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 25,76</t>
+          <t>-6,88; 25,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 21,39</t>
+          <t>-16,31; 22,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 24,76</t>
+          <t>-22,66; 20,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,99; —</t>
+          <t>-64,22; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 7,33</t>
+          <t>-7,73; 7,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 15,13</t>
+          <t>-3,75; 14,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 5,33</t>
+          <t>-10,6; 5,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 12,79</t>
+          <t>-0,72; 13,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,2; 126,82</t>
+          <t>-57,12; 126,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 173,28</t>
+          <t>-23,5; 157,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,88; 64,52</t>
+          <t>-58,14; 66,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 633,52</t>
+          <t>-26,35; 666,42</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 5,67</t>
+          <t>-18,07; 4,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 15,52</t>
+          <t>-12,43; 17,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 14,34</t>
+          <t>-15,55; 15,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 10,19</t>
+          <t>-11,65; 9,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 195,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,39; 210,74</t>
+          <t>-58,43; 252,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-72,26; 239,05</t>
+          <t>-73,26; 245,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,24; 389,56</t>
+          <t>-81,02; 344,24</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 4,63</t>
+          <t>-7,1; 4,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 12,27</t>
+          <t>-1,72; 11,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 5,05</t>
+          <t>-7,44; 6,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 8,97</t>
+          <t>-2,34; 9,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,51; 63,32</t>
+          <t>-55,59; 57,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 122,81</t>
+          <t>-12,74; 110,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 57,54</t>
+          <t>-47,42; 70,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 250,83</t>
+          <t>-35,55; 262,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 15,96</t>
+          <t>-10,75; 16,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 25,8</t>
+          <t>-6,25; 23,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 22,75</t>
+          <t>-18,22; 22,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 20,46</t>
+          <t>-23,64; 22,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-64,22; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 7,33</t>
+          <t>-7,38; 7,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 14,73</t>
+          <t>-3,01; 14,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 5,47</t>
+          <t>-9,96; 4,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 13,27</t>
+          <t>-0,97; 13,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,12; 126,55</t>
+          <t>-54,65; 134,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 157,29</t>
+          <t>-18,58; 145,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 66,94</t>
+          <t>-59,71; 59,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 666,42</t>
+          <t>-32,28; 723,39</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 4,96</t>
+          <t>-19,89; 4,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 17,88</t>
+          <t>-10,46; 17,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 15,24</t>
+          <t>-14,44; 14,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 9,24</t>
+          <t>-11,13; 9,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 133,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,43; 252,64</t>
+          <t>-54,74; 248,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,26; 245,97</t>
+          <t>-71,0; 211,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,02; 344,24</t>
+          <t>-79,49; 320,2</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,28</t>
+          <t>-6,79; 4,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 11,24</t>
+          <t>-1,7; 11,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 6,3</t>
+          <t>-7,98; 5,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 9,35</t>
+          <t>-2,05; 9,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 57,54</t>
+          <t>-54,24; 67,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 110,81</t>
+          <t>-11,11; 118,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 70,09</t>
+          <t>-47,57; 62,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 262,05</t>
+          <t>-31,22; 280,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 16,12</t>
+          <t>-10,58; 16,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 23,77</t>
+          <t>-7,72; 25,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 22,68</t>
+          <t>-19,83; 21,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 22,14</t>
+          <t>-24,02; 26,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,99; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>131,22%</t>
+          <t>135,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 7,82</t>
+          <t>-7,38; 7,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 14,11</t>
+          <t>-3,9; 15,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 4,85</t>
+          <t>-10,34; 5,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 13,88</t>
+          <t>-0,17; 9,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 134,71</t>
+          <t>-55,2; 126,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 145,26</t>
+          <t>-21,17; 173,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 59,44</t>
+          <t>-58,88; 64,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 723,39</t>
+          <t>-20,24; 622,27</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>-0,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 4,32</t>
+          <t>-16,91; 5,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 17,12</t>
+          <t>-12,68; 15,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 14,28</t>
+          <t>-15,59; 14,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 9,66</t>
+          <t>-10,91; 9,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 133,69</t>
+          <t>-100,0; 195,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 248,29</t>
+          <t>-62,39; 210,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-71,0; 211,71</t>
+          <t>-72,26; 239,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,49; 320,2</t>
+          <t>-79,89; 370,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 4,72</t>
+          <t>-7,12; 4,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,68</t>
+          <t>-1,44; 12,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 5,69</t>
+          <t>-7,9; 5,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 9,4</t>
+          <t>-2,1; 7,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 67,83</t>
+          <t>-56,51; 63,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 118,22</t>
+          <t>-10,51; 122,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 62,0</t>
+          <t>-49,64; 57,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 280,6</t>
+          <t>-30,09; 227,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,185 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,17</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,95</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>123,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.7245360673802178</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.627354334912559</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.338868400923742</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.1150160015149462</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.4826144491026876</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.724443573343881</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>2.41382100176632</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.0350922521127246</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-10,58; 16,08</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,72; 25,76</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-19,83; 21,39</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-24,02; 26,6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-71,99; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.760044761198739</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.9592095292384464</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.9755656829980088</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.549688844884761</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.8240407970811527</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.70957953614152</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.741102578184596</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.48014004703354</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.897870243099864</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,31</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>39,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-18,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>135,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,38; 7,33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,9; 15,13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-10,34; 5,33</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 9,96</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-55,2; 126,82</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-21,17; 173,28</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-58,88; 64,52</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-20,24; 622,27</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.03079323082659235</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9140672246339753</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.4071027457909052</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.889169329525856</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.01663121129501859</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.3352296176419797</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1803737688450465</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1.224454760827107</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-7,13</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-55,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-3,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-0,71%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.30748962586259</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.038065414346401</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.803182221660911</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.01119156952751076</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5359015211345574</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3472366988801273</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6178082090148035</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1324164669534367</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-16,91; 5,67</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-12,68; 15,52</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-15,59; 14,34</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,91; 9,3</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 195,91</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-62,39; 210,74</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-72,26; 239,05</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-79,89; 370,64</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.370883648187153</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.834704170360112</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.00594914119085</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.252697880511654</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.307055403679315</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.378643472573585</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7493030874265284</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>5.000129821076711</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +805,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-13,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-10,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.127978588423867</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3167768639294508</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1021137989483355</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.1031751798816663</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.7401182841026457</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.09523760541061045</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.04389009067283765</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.04793160704313394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-7,12; 4,63</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; 12,27</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,9; 5,05</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 7,83</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-56,51; 63,32</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-10,51; 122,81</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-49,64; 57,54</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-30,09; 227,5</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.949955224906738</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.130269252182698</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.742307262127435</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.900595861861438</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6630749834933373</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7724272944658633</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7962191256444974</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.1028390618761605</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.479018475649081</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.598937685228356</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.769498870438591</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.6068414599235361</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2.185548045186154</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.61231667283082</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>4.897938019335012</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3955935948229485</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9816484228462503</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.04114815518994029</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.6224172174968312</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1945269858297459</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3601232879456041</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.01908667176998525</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.4877995476668828</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.566411612211065</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.5714849506736561</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.224466549254025</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.521538003841174</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5778503107133339</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1963167348143218</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4424791810761384</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.307380863168938</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8150462635500297</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.501416457233394</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.172567130902131</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.763268279733986</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6340242537233938</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.185904831914015</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.8146357680153501</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.379096806588316</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1003,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
